--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1076,16 +1076,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -893,10 +893,10 @@
         <v>4.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,28 +1052,28 @@
         <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
         <v>1.48</v>
@@ -1088,19 +1088,19 @@
         <v>1.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.5</v>
       </c>
-      <c r="U4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="AB4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.05</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
         <v>1.97</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>3.89</v>
@@ -1082,10 +1082,10 @@
         <v>2.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
         <v>4.8</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
         <v>1.97</v>
@@ -1046,13 +1046,13 @@
         <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
         <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.89</v>
+        <v>3.75</v>
       </c>
       <c r="R4" t="n">
         <v>1.9</v>
@@ -1061,19 +1061,19 @@
         <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V4" t="n">
         <v>1.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.49</v>
@@ -1082,25 +1082,25 @@
         <v>2.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AC4" t="n">
         <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
         <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>3.75</v>
@@ -1064,7 +1064,7 @@
         <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V4" t="n">
         <v>1.26</v>
@@ -1085,13 +1085,13 @@
         <v>2.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
         <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
         <v>1.02</v>
@@ -1100,7 +1100,7 @@
         <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AK4" t="n">
         <v>1.36</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
         <v>2.5</v>
@@ -1070,7 +1070,7 @@
         <v>1.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.05</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1097,7 +1097,7 @@
         <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AG4" t="n">
         <v>1.73</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
         <v>1.36</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
         <v>1.97</v>
@@ -1046,16 +1046,16 @@
         <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="P4" t="n">
         <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S4" t="n">
         <v>1.5</v>
@@ -1094,7 +1094,7 @@
         <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
         <v>2.02</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.9</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.96</v>
       </c>
       <c r="P4" t="n">
         <v>2.5</v>
@@ -1055,7 +1055,7 @@
         <v>3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S4" t="n">
         <v>1.5</v>
@@ -1097,10 +1097,10 @@
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1073,7 +1073,7 @@
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.49</v>
@@ -1091,16 +1091,16 @@
         <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>4.83</v>
+        <v>4.75</v>
       </c>
       <c r="Q3" t="n">
         <v>2.1</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
         <v>1.97</v>
@@ -1049,7 +1049,7 @@
         <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Q4" t="n">
         <v>3.7</v>
@@ -1070,7 +1070,7 @@
         <v>1.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
         <v>1.1</v>
@@ -1091,13 +1091,13 @@
         <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
         <v>1.73</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK4" t="n">
         <v>1.36</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="O3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>4.75</v>
+        <v>3.69</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R3" t="n">
         <v>2.1</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="O4" t="n">
         <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="R4" t="n">
         <v>1.95</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="U4" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="V4" t="n">
         <v>1.26</v>
@@ -1076,25 +1076,25 @@
         <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AB4" t="n">
         <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
         <v>1.97</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q4" t="n">
         <v>3.83</v>
@@ -1058,16 +1058,16 @@
         <v>1.95</v>
       </c>
       <c r="S4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T4" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
         <v>3.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
@@ -1082,22 +1082,22 @@
         <v>2.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AB4" t="n">
         <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE4" t="n">
         <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
         <v>1.73</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -728,58 +728,58 @@
         <v>1.36</v>
       </c>
       <c r="O2" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="P2" t="n">
-        <v>7.95</v>
+        <v>6.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
         <v>1.75</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
         <v>3.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
         <v>1.35</v>
@@ -905,43 +905,43 @@
         <v>2.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.88</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.05</v>
-      </c>
       <c r="P4" t="n">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="Q4" t="n">
         <v>3.83</v>
@@ -1067,7 +1067,7 @@
         <v>3.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
@@ -1079,19 +1079,19 @@
         <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
         <v>1.05</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -725,43 +725,43 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="O2" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="P2" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
         <v>1.11</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="AA2" t="n">
         <v>1.7</v>
@@ -770,19 +770,19 @@
         <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
         <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>3.69</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T3" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,49 +1052,49 @@
         <v>2.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="S4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
         <v>3.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AB4" t="n">
         <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>2.1</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -714,14 +714,14 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '68']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46196.5</v>
@@ -861,26 +861,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74', '87']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46196.58333333334</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1043,58 +1043,58 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.21</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
         <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S4" t="n">
         <v>1.53</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="U4" t="n">
         <v>3.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
         <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
         <v>2.1</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AK4" t="n">
         <v>1.36</v>

--- a/jogos_2026-06-23.xlsx
+++ b/jogos_2026-06-23.xlsx
@@ -1023,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46196.83333333334</v>
